--- a/data/populasi/populasi.xlsx
+++ b/data/populasi/populasi.xlsx
@@ -1487,7 +1487,7 @@
       </c>
       <c r="B2" s="12" t="inlineStr">
         <is>
-          <t>PT. SARI SAWIT SEJAHTERA - APING riski</t>
+          <t xml:space="preserve">PT. SARI SAWIT SEJAHTERA - APING </t>
         </is>
       </c>
       <c r="C2" s="12" t="inlineStr">
